--- a/Pipe.xlsx
+++ b/Pipe.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/edith_bah_orange_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/edith_bah_orange_com/Documents/Attachments/Bureau/Nouveau dossier/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDC94E0F-CFD3-494C-97B8-7985E16C9756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{BDC94E0F-CFD3-494C-97B8-7985E16C9756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47986C21-44A2-4435-B561-2572492B1419}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{84233975-2056-46F2-B183-E35E29C39690}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$Q$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil2!$A$1:$Q$96</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="252">
   <si>
     <t>ID DOSSIER</t>
   </si>
@@ -197,12 +197,6 @@
     <t>SYTHD260225</t>
   </si>
   <si>
-    <t>BRIDGEBANK</t>
-  </si>
-  <si>
-    <t>GRAND-BASSAM</t>
-  </si>
-  <si>
     <t>T0</t>
   </si>
   <si>
@@ -308,12 +302,6 @@
     <t>OUMME</t>
   </si>
   <si>
-    <t>PROJET E-JUSTICE</t>
-  </si>
-  <si>
-    <t>ABOISSO//VOIE INCONNUE/</t>
-  </si>
-  <si>
     <t>BUVPN260162</t>
   </si>
   <si>
@@ -371,21 +359,12 @@
     <t>YAMOUSSOUKRO ZONE INDUSTRIELLE</t>
   </si>
   <si>
-    <t>CLINIQUE DES YEUX LASERS</t>
-  </si>
-  <si>
-    <t>PLATEAU INDENIE</t>
-  </si>
-  <si>
     <t>ftto</t>
   </si>
   <si>
     <t>Principale (avec backup)</t>
   </si>
   <si>
-    <t>SYTHD260251</t>
-  </si>
-  <si>
     <t>Parametrage facturation</t>
   </si>
   <si>
@@ -404,9 +383,6 @@
     <t>fo_virage</t>
   </si>
   <si>
-    <t>XXXXXXXXXXXXX</t>
-  </si>
-  <si>
     <t>MINISTERE DU LOGEMENT ET URBANISME</t>
   </si>
   <si>
@@ -740,15 +716,6 @@
     <t>COCODY ANGRE</t>
   </si>
   <si>
-    <t>COMPAGNIE HOTELIERE DE LA LAGUNE</t>
-  </si>
-  <si>
-    <t>ABIDJAN-MARCORY//VOIE INCONNUE/CONTACT CLT 0707291110</t>
-  </si>
-  <si>
-    <t>SYTHD210190</t>
-  </si>
-  <si>
     <t>BO Homologation: Saisie GAIA LSI</t>
   </si>
   <si>
@@ -785,9 +752,6 @@
     <t>STE GAUFF</t>
   </si>
   <si>
-    <t>SIE: Pilote</t>
-  </si>
-  <si>
     <t>BANQUE MONDIALE</t>
   </si>
   <si>
@@ -795,6 +759,45 @@
   </si>
   <si>
     <t>Temporaire</t>
+  </si>
+  <si>
+    <t>Support IP: Correction</t>
+  </si>
+  <si>
+    <t>BO Homologation: Mise en service GAIA</t>
+  </si>
+  <si>
+    <t>SYTHD260255</t>
+  </si>
+  <si>
+    <t>STE HOTEL AZALAI</t>
+  </si>
+  <si>
+    <t>MARCORY BOULEVARD VGE</t>
+  </si>
+  <si>
+    <t>LSI Gold</t>
+  </si>
+  <si>
+    <t>STE TERRA (AGL)</t>
+  </si>
+  <si>
+    <t>TREICHVILLE QUAI 17</t>
+  </si>
+  <si>
+    <t>ETS BANQUE SAHELO SAHARIENNE POUR L'INVESTISSEMENT ET LE COMMERCE EN COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>ABOBO</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie GAIA</t>
+  </si>
+  <si>
+    <t>OFFICE NATIONAL DE LA PROTECTION CIVILE</t>
+  </si>
+  <si>
+    <t>ADJAME</t>
   </si>
 </sst>
 </file>
@@ -1178,8 +1181,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8238D3-B575-43CA-98BB-24C740F8E091}">
-  <dimension ref="A1:Q94"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FFA819-8BFF-403A-B4F1-D40172154CE8}">
+  <dimension ref="A1:Q96"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
@@ -1608,46 +1611,46 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>64761746</v>
+        <v>64775381</v>
       </c>
       <c r="B9" s="2">
-        <v>46185.375196759262</v>
+        <v>46185.497025462966</v>
       </c>
       <c r="C9">
-        <v>70278563</v>
+        <v>70322089</v>
       </c>
       <c r="D9" s="2">
-        <v>46281.689027777778</v>
+        <v>46282.363738425927</v>
       </c>
       <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9">
+        <v>757500782</v>
+      </c>
+      <c r="H9" t="s">
         <v>57</v>
       </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9">
-        <v>749503436</v>
-      </c>
-      <c r="H9" t="s">
-        <v>52</v>
-      </c>
       <c r="I9" t="s">
         <v>25</v>
       </c>
       <c r="J9" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="K9" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="L9" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="M9" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="N9" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O9" t="s">
         <v>25</v>
@@ -1655,40 +1658,40 @@
       <c r="P9" t="s">
         <v>25</v>
       </c>
-      <c r="Q9">
-        <v>2721712170</v>
+      <c r="Q9" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>64775381</v>
+        <v>64986217</v>
       </c>
       <c r="B10" s="2">
-        <v>46185.497025462966</v>
+        <v>46189.594629629632</v>
       </c>
       <c r="C10">
-        <v>70322089</v>
+        <v>70175612</v>
       </c>
       <c r="D10" s="2">
-        <v>46282.363738425927</v>
+        <v>46280.434374999997</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F10" t="s">
         <v>58</v>
       </c>
       <c r="G10">
-        <v>757500782</v>
+        <v>707109668</v>
       </c>
       <c r="H10" t="s">
         <v>59</v>
       </c>
-      <c r="I10" t="s">
-        <v>25</v>
+      <c r="I10">
+        <v>4120446</v>
       </c>
       <c r="J10" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="K10" t="s">
         <v>20</v>
@@ -1697,10 +1700,10 @@
         <v>37</v>
       </c>
       <c r="M10" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="N10" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O10" t="s">
         <v>25</v>
@@ -1709,36 +1712,36 @@
         <v>25</v>
       </c>
       <c r="Q10" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>64986217</v>
+        <v>64987973</v>
       </c>
       <c r="B11" s="2">
-        <v>46189.594629629632</v>
+        <v>46189.606724537036</v>
       </c>
       <c r="C11">
-        <v>70175612</v>
+        <v>70147119</v>
       </c>
       <c r="D11" s="2">
-        <v>46280.434374999997</v>
+        <v>46279.754328703704</v>
       </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>707109668</v>
       </c>
       <c r="H11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I11">
-        <v>4120446</v>
+        <v>4120436</v>
       </c>
       <c r="J11" t="s">
         <v>19</v>
@@ -1753,7 +1756,7 @@
         <v>22</v>
       </c>
       <c r="N11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O11" t="s">
         <v>25</v>
@@ -1767,34 +1770,34 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>64987973</v>
+        <v>65351507</v>
       </c>
       <c r="B12" s="2">
-        <v>46189.606724537036</v>
+        <v>46196.572060185186</v>
       </c>
       <c r="C12">
-        <v>70147119</v>
+        <v>69452838</v>
       </c>
       <c r="D12" s="2">
-        <v>46279.754328703704</v>
+        <v>46267.515162037038</v>
       </c>
       <c r="E12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" t="s">
         <v>63</v>
       </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
       <c r="G12">
-        <v>707109668</v>
+        <v>2299777247</v>
       </c>
       <c r="H12" t="s">
-        <v>61</v>
-      </c>
-      <c r="I12">
-        <v>4120436</v>
+        <v>64</v>
+      </c>
+      <c r="I12" t="s">
+        <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K12" t="s">
         <v>20</v>
@@ -1806,7 +1809,7 @@
         <v>22</v>
       </c>
       <c r="N12" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O12" t="s">
         <v>25</v>
@@ -1815,86 +1818,86 @@
         <v>25</v>
       </c>
       <c r="Q12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>65351507</v>
+        <v>65828465</v>
       </c>
       <c r="B13" s="2">
-        <v>46196.572060185186</v>
+        <v>46205.656736111108</v>
       </c>
       <c r="C13">
-        <v>69452838</v>
+        <v>69850886</v>
       </c>
       <c r="D13" s="2">
-        <v>46267.515162037038</v>
+        <v>46274.524675925924</v>
       </c>
       <c r="E13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13">
+        <v>708086472</v>
+      </c>
+      <c r="H13" t="s">
         <v>68</v>
       </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13">
-        <v>2299777247</v>
-      </c>
-      <c r="H13" t="s">
-        <v>66</v>
-      </c>
       <c r="I13" t="s">
         <v>25</v>
       </c>
       <c r="J13" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K13" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="L13" t="s">
         <v>37</v>
       </c>
       <c r="M13" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="N13" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O13" t="s">
         <v>25</v>
       </c>
-      <c r="P13" t="s">
-        <v>25</v>
+      <c r="P13">
+        <v>0</v>
       </c>
       <c r="Q13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>65828465</v>
+        <v>65833190</v>
       </c>
       <c r="B14" s="2">
-        <v>46205.656736111108</v>
+        <v>46205.688449074078</v>
       </c>
       <c r="C14">
-        <v>69850886</v>
+        <v>70584470</v>
       </c>
       <c r="D14" s="2">
-        <v>46274.524675925924</v>
+        <v>46286.503240740742</v>
       </c>
       <c r="E14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>708086472</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I14" t="s">
         <v>25</v>
@@ -1903,7 +1906,7 @@
         <v>36</v>
       </c>
       <c r="K14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L14" t="s">
         <v>37</v>
@@ -1912,7 +1915,7 @@
         <v>41</v>
       </c>
       <c r="N14" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O14" t="s">
         <v>25</v>
@@ -1926,28 +1929,28 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>65833190</v>
+        <v>65835797</v>
       </c>
       <c r="B15" s="2">
-        <v>46205.688449074078</v>
+        <v>46205.706365740742</v>
       </c>
       <c r="C15">
-        <v>66321201</v>
+        <v>70211747</v>
       </c>
       <c r="D15" s="2">
-        <v>46213.652453703704</v>
+        <v>46280.703703703701</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G15">
         <v>708086472</v>
       </c>
       <c r="H15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I15" t="s">
         <v>25</v>
@@ -1956,7 +1959,7 @@
         <v>36</v>
       </c>
       <c r="K15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L15" t="s">
         <v>37</v>
@@ -1965,7 +1968,7 @@
         <v>41</v>
       </c>
       <c r="N15" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O15" t="s">
         <v>25</v>
@@ -1974,33 +1977,33 @@
         <v>0</v>
       </c>
       <c r="Q15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>65835797</v>
+        <v>66519717</v>
       </c>
       <c r="B16" s="2">
-        <v>46205.706365740742</v>
+        <v>46217.478252314817</v>
       </c>
       <c r="C16">
-        <v>70211747</v>
+        <v>68299637</v>
       </c>
       <c r="D16" s="2">
-        <v>46280.703703703701</v>
+        <v>46247.65079861111</v>
       </c>
       <c r="E16" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G16">
-        <v>708086472</v>
+        <v>708223012</v>
       </c>
       <c r="H16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s">
         <v>25</v>
@@ -2009,51 +2012,51 @@
         <v>36</v>
       </c>
       <c r="K16" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="L16" t="s">
         <v>37</v>
       </c>
       <c r="M16" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="N16" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O16" t="s">
         <v>25</v>
       </c>
-      <c r="P16">
-        <v>0</v>
+      <c r="P16" s="1">
+        <v>529849</v>
       </c>
       <c r="Q16" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>66519717</v>
+        <v>66519778</v>
       </c>
       <c r="B17" s="2">
-        <v>46217.478252314817</v>
+        <v>46217.478402777779</v>
       </c>
       <c r="C17">
-        <v>68299637</v>
+        <v>70339369</v>
       </c>
       <c r="D17" s="2">
-        <v>46247.65079861111</v>
+        <v>46282.517500000002</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G17">
         <v>708223012</v>
       </c>
       <c r="H17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s">
         <v>25</v>
@@ -2071,42 +2074,42 @@
         <v>22</v>
       </c>
       <c r="N17" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O17" t="s">
         <v>25</v>
       </c>
       <c r="P17" s="1">
-        <v>529849</v>
+        <v>821949</v>
       </c>
       <c r="Q17" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>66519778</v>
+        <v>66521727</v>
       </c>
       <c r="B18" s="2">
-        <v>46217.478402777779</v>
+        <v>46217.490879629629</v>
       </c>
       <c r="C18">
-        <v>70339369</v>
+        <v>68301396</v>
       </c>
       <c r="D18" s="2">
-        <v>46282.517500000002</v>
+        <v>46247.661053240743</v>
       </c>
       <c r="E18" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G18">
         <v>708223012</v>
       </c>
       <c r="H18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I18" t="s">
         <v>25</v>
@@ -2130,36 +2133,36 @@
         <v>25</v>
       </c>
       <c r="P18" s="1">
-        <v>821949</v>
+        <v>567271</v>
       </c>
       <c r="Q18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>66521727</v>
+        <v>66522786</v>
       </c>
       <c r="B19" s="2">
-        <v>46217.490879629629</v>
+        <v>46217.497870370367</v>
       </c>
       <c r="C19">
-        <v>68301396</v>
+        <v>68290469</v>
       </c>
       <c r="D19" s="2">
-        <v>46247.661053240743</v>
+        <v>46247.594166666669</v>
       </c>
       <c r="E19" t="s">
         <v>47</v>
       </c>
       <c r="F19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G19">
         <v>708223012</v>
       </c>
       <c r="H19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I19" t="s">
         <v>25</v>
@@ -2183,30 +2186,30 @@
         <v>25</v>
       </c>
       <c r="P19" s="1">
-        <v>567271</v>
+        <v>568400</v>
       </c>
       <c r="Q19" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>66522786</v>
+        <v>66526010</v>
       </c>
       <c r="B20" s="2">
-        <v>46217.497870370367</v>
+        <v>46217.520474537036</v>
       </c>
       <c r="C20">
-        <v>68290469</v>
+        <v>68292637</v>
       </c>
       <c r="D20" s="2">
-        <v>46247.594166666669</v>
+        <v>46247.608402777776</v>
       </c>
       <c r="E20" t="s">
         <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G20">
         <v>708223012</v>
@@ -2218,7 +2221,7 @@
         <v>25</v>
       </c>
       <c r="J20" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K20" t="s">
         <v>20</v>
@@ -2236,42 +2239,42 @@
         <v>25</v>
       </c>
       <c r="P20" s="1">
-        <v>568400</v>
+        <v>651639</v>
       </c>
       <c r="Q20" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>66526010</v>
+        <v>66533655</v>
       </c>
       <c r="B21" s="2">
-        <v>46217.520474537036</v>
+        <v>46217.582395833335</v>
       </c>
       <c r="C21">
-        <v>68292637</v>
+        <v>70584833</v>
       </c>
       <c r="D21" s="2">
-        <v>46247.608402777776</v>
+        <v>46286.504745370374</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G21">
         <v>708223012</v>
       </c>
       <c r="H21" t="s">
-        <v>87</v>
+        <v>173</v>
       </c>
       <c r="I21" t="s">
         <v>25</v>
       </c>
       <c r="J21" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K21" t="s">
         <v>20</v>
@@ -2289,42 +2292,42 @@
         <v>25</v>
       </c>
       <c r="P21" s="1">
-        <v>651639</v>
+        <v>208139</v>
       </c>
       <c r="Q21" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>66533655</v>
+        <v>66538425</v>
       </c>
       <c r="B22" s="2">
-        <v>46217.582395833335</v>
+        <v>46217.616307870368</v>
       </c>
       <c r="C22">
-        <v>69709054</v>
+        <v>69737392</v>
       </c>
       <c r="D22" s="2">
-        <v>46272.403425925928</v>
+        <v>46272.622245370374</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="F22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G22">
         <v>708223012</v>
       </c>
       <c r="H22" t="s">
-        <v>89</v>
-      </c>
-      <c r="I22">
-        <v>1960576</v>
+        <v>88</v>
+      </c>
+      <c r="I22" t="s">
+        <v>25</v>
       </c>
       <c r="J22" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="K22" t="s">
         <v>20</v>
@@ -2333,45 +2336,45 @@
         <v>37</v>
       </c>
       <c r="M22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O22" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22" s="1">
+        <v>602789</v>
+      </c>
+      <c r="Q22" t="s">
         <v>80</v>
-      </c>
-      <c r="N22" t="s">
-        <v>56</v>
-      </c>
-      <c r="O22" t="s">
-        <v>25</v>
-      </c>
-      <c r="P22" s="1">
-        <v>208139</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>66538425</v>
+        <v>66539529</v>
       </c>
       <c r="B23" s="2">
-        <v>46217.616307870368</v>
+        <v>46217.623819444445</v>
       </c>
       <c r="C23">
-        <v>69737392</v>
+        <v>69898003</v>
       </c>
       <c r="D23" s="2">
-        <v>46272.622245370374</v>
+        <v>46275.392500000002</v>
       </c>
       <c r="E23" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G23">
         <v>708223012</v>
       </c>
       <c r="H23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I23" t="s">
         <v>25</v>
@@ -2395,42 +2398,42 @@
         <v>25</v>
       </c>
       <c r="P23" s="1">
-        <v>602789</v>
+        <v>694965</v>
       </c>
       <c r="Q23" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>66539529</v>
+        <v>66541204</v>
       </c>
       <c r="B24" s="2">
-        <v>46217.623819444445</v>
+        <v>46217.635231481479</v>
       </c>
       <c r="C24">
-        <v>69898003</v>
+        <v>68716037</v>
       </c>
       <c r="D24" s="2">
-        <v>46275.392500000002</v>
+        <v>46254.347962962966</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="F24" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G24">
         <v>708223012</v>
       </c>
       <c r="H24" t="s">
-        <v>95</v>
-      </c>
-      <c r="I24" t="s">
-        <v>25</v>
+        <v>92</v>
+      </c>
+      <c r="I24">
+        <v>1960436</v>
       </c>
       <c r="J24" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="K24" t="s">
         <v>20</v>
@@ -2442,48 +2445,48 @@
         <v>22</v>
       </c>
       <c r="N24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O24" t="s">
         <v>25</v>
       </c>
       <c r="P24" s="1">
-        <v>694965</v>
+        <v>516531</v>
       </c>
       <c r="Q24" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>66541204</v>
+        <v>66542670</v>
       </c>
       <c r="B25" s="2">
-        <v>46217.635231481479</v>
+        <v>46217.645162037035</v>
       </c>
       <c r="C25">
-        <v>68716037</v>
+        <v>69739187</v>
       </c>
       <c r="D25" s="2">
-        <v>46254.347962962966</v>
+        <v>46272.634143518517</v>
       </c>
       <c r="E25" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="F25" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G25">
         <v>708223012</v>
       </c>
       <c r="H25" t="s">
-        <v>96</v>
-      </c>
-      <c r="I25">
-        <v>1960436</v>
+        <v>95</v>
+      </c>
+      <c r="I25" t="s">
+        <v>25</v>
       </c>
       <c r="J25" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="K25" t="s">
         <v>20</v>
@@ -2495,42 +2498,42 @@
         <v>22</v>
       </c>
       <c r="N25" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O25" t="s">
         <v>25</v>
       </c>
       <c r="P25" s="1">
-        <v>516531</v>
+        <v>1549325</v>
       </c>
       <c r="Q25" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>66542670</v>
+        <v>66544270</v>
       </c>
       <c r="B26" s="2">
-        <v>46217.645162037035</v>
+        <v>46217.656736111108</v>
       </c>
       <c r="C26">
-        <v>69739187</v>
+        <v>69739645</v>
       </c>
       <c r="D26" s="2">
-        <v>46272.634143518517</v>
+        <v>46272.637199074074</v>
       </c>
       <c r="E26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G26">
         <v>708223012</v>
       </c>
       <c r="H26" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I26" t="s">
         <v>25</v>
@@ -2554,36 +2557,36 @@
         <v>25</v>
       </c>
       <c r="P26" s="1">
-        <v>1549325</v>
+        <v>919178</v>
       </c>
       <c r="Q26" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>66544270</v>
+        <v>66886330</v>
       </c>
       <c r="B27" s="2">
-        <v>46217.656736111108</v>
+        <v>46223.635370370372</v>
       </c>
       <c r="C27">
-        <v>69739645</v>
+        <v>68062464</v>
       </c>
       <c r="D27" s="2">
-        <v>46272.637199074074</v>
+        <v>46244.478368055556</v>
       </c>
       <c r="E27" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="F27" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G27">
-        <v>708223012</v>
+        <v>102571205</v>
       </c>
       <c r="H27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I27" t="s">
         <v>25</v>
@@ -2607,101 +2610,98 @@
         <v>25</v>
       </c>
       <c r="P27" s="1">
-        <v>919178</v>
+        <v>2500000</v>
       </c>
       <c r="Q27" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>66886330</v>
+        <v>66962325</v>
       </c>
       <c r="B28" s="2">
-        <v>46223.635370370372</v>
+        <v>46224.722592592596</v>
       </c>
       <c r="C28">
-        <v>68062464</v>
+        <v>70355294</v>
       </c>
       <c r="D28" s="2">
-        <v>46244.478368055556</v>
+        <v>46282.63994212963</v>
       </c>
       <c r="E28" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G28">
-        <v>102571205</v>
+        <v>709405439</v>
       </c>
       <c r="H28" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I28" t="s">
         <v>25</v>
       </c>
       <c r="J28" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="K28" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="L28" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="M28" t="s">
         <v>22</v>
       </c>
-      <c r="N28" t="s">
-        <v>23</v>
-      </c>
       <c r="O28" t="s">
         <v>25</v>
       </c>
-      <c r="P28" s="1">
-        <v>2500000</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>30</v>
+      <c r="P28" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28">
+        <v>2721712313</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>66962325</v>
+        <v>67001646</v>
       </c>
       <c r="B29" s="2">
-        <v>46224.722592592596</v>
+        <v>46225.547824074078</v>
       </c>
       <c r="C29">
-        <v>70355294</v>
+        <v>69746219</v>
       </c>
       <c r="D29" s="2">
-        <v>46282.63994212963</v>
+        <v>46272.681458333333</v>
       </c>
       <c r="E29" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="F29" t="s">
+        <v>103</v>
+      </c>
+      <c r="G29">
+        <v>799146768</v>
+      </c>
+      <c r="H29" t="s">
         <v>104</v>
       </c>
-      <c r="G29">
-        <v>709405439</v>
-      </c>
-      <c r="H29" t="s">
-        <v>105</v>
-      </c>
       <c r="I29" t="s">
         <v>25</v>
       </c>
       <c r="J29" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="K29" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="L29" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="M29" t="s">
         <v>22</v>
@@ -2712,49 +2712,49 @@
       <c r="O29" t="s">
         <v>25</v>
       </c>
-      <c r="P29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q29">
-        <v>2721712313</v>
+      <c r="P29" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>67001646</v>
+        <v>67775984</v>
       </c>
       <c r="B30" s="2">
-        <v>46225.547824074078</v>
+        <v>46238.687002314815</v>
       </c>
       <c r="C30">
-        <v>69746219</v>
+        <v>69778665</v>
       </c>
       <c r="D30" s="2">
-        <v>46272.681458333333</v>
+        <v>46273.441018518519</v>
       </c>
       <c r="E30" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="F30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G30">
-        <v>799146768</v>
+        <v>566173307</v>
       </c>
       <c r="H30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I30" t="s">
         <v>25</v>
       </c>
       <c r="J30" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K30" t="s">
         <v>20</v>
       </c>
       <c r="L30" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M30" t="s">
         <v>22</v>
@@ -2766,51 +2766,51 @@
         <v>25</v>
       </c>
       <c r="P30" s="1">
-        <v>6000000</v>
+        <v>500000</v>
       </c>
       <c r="Q30" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>67062562</v>
+        <v>67840097</v>
       </c>
       <c r="B31" s="2">
-        <v>46226.530300925922</v>
+        <v>46239.654745370368</v>
       </c>
       <c r="C31">
-        <v>70445475</v>
+        <v>70584305</v>
       </c>
       <c r="D31" s="2">
-        <v>46283.713576388887</v>
+        <v>46286.502453703702</v>
       </c>
       <c r="E31" t="s">
-        <v>114</v>
+        <v>239</v>
       </c>
       <c r="F31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G31">
-        <v>720181818</v>
+        <v>747202564</v>
       </c>
       <c r="H31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I31" t="s">
         <v>25</v>
       </c>
       <c r="J31" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="K31" t="s">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="L31" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="M31" t="s">
-        <v>112</v>
+        <v>22</v>
       </c>
       <c r="N31" t="s">
         <v>23</v>
@@ -2818,108 +2818,108 @@
       <c r="O31" t="s">
         <v>25</v>
       </c>
-      <c r="P31" s="1">
-        <v>1862401</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>113</v>
+      <c r="P31" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q31">
+        <v>2722580585</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>67775984</v>
+        <v>67847645</v>
       </c>
       <c r="B32" s="2">
-        <v>46238.687002314815</v>
+        <v>46239.712222222224</v>
       </c>
       <c r="C32">
-        <v>69778665</v>
+        <v>69874339</v>
       </c>
       <c r="D32" s="2">
-        <v>46273.441018518519</v>
+        <v>46274.696574074071</v>
       </c>
       <c r="E32" t="s">
         <v>47</v>
       </c>
       <c r="F32" t="s">
+        <v>113</v>
+      </c>
+      <c r="G32">
+        <v>777313773</v>
+      </c>
+      <c r="H32" t="s">
+        <v>114</v>
+      </c>
+      <c r="I32" t="s">
+        <v>25</v>
+      </c>
+      <c r="J32" t="s">
         <v>115</v>
       </c>
-      <c r="G32">
-        <v>566173307</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="K32" t="s">
+        <v>112</v>
+      </c>
+      <c r="L32" t="s">
+        <v>53</v>
+      </c>
+      <c r="M32" t="s">
+        <v>22</v>
+      </c>
+      <c r="N32" t="s">
+        <v>23</v>
+      </c>
+      <c r="O32" t="s">
+        <v>25</v>
+      </c>
+      <c r="P32" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q32" t="s">
         <v>116</v>
-      </c>
-      <c r="I32" t="s">
-        <v>25</v>
-      </c>
-      <c r="J32" t="s">
-        <v>36</v>
-      </c>
-      <c r="K32" t="s">
-        <v>20</v>
-      </c>
-      <c r="L32" t="s">
-        <v>37</v>
-      </c>
-      <c r="M32" t="s">
-        <v>22</v>
-      </c>
-      <c r="N32" t="s">
-        <v>23</v>
-      </c>
-      <c r="O32" t="s">
-        <v>25</v>
-      </c>
-      <c r="P32" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>67840097</v>
+        <v>68233792</v>
       </c>
       <c r="B33" s="2">
-        <v>46239.654745370368</v>
+        <v>46246.680034722223</v>
       </c>
       <c r="C33">
-        <v>70367016</v>
+        <v>69930336</v>
       </c>
       <c r="D33" s="2">
-        <v>46282.720451388886</v>
+        <v>46275.644270833334</v>
       </c>
       <c r="E33" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F33" t="s">
         <v>117</v>
       </c>
       <c r="G33">
-        <v>747202564</v>
+        <v>584572192</v>
       </c>
       <c r="H33" t="s">
         <v>118</v>
       </c>
-      <c r="I33" t="s">
-        <v>25</v>
+      <c r="I33">
+        <v>4118436</v>
       </c>
       <c r="J33" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="K33" t="s">
         <v>119</v>
       </c>
       <c r="L33" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="M33" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="N33" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O33" t="s">
         <v>25</v>
@@ -2928,57 +2928,57 @@
         <v>25</v>
       </c>
       <c r="Q33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>67847645</v>
+        <v>68233824</v>
       </c>
       <c r="B34" s="2">
-        <v>46239.712222222224</v>
+        <v>46246.680150462962</v>
       </c>
       <c r="C34">
-        <v>69874339</v>
+        <v>69930019</v>
       </c>
       <c r="D34" s="2">
-        <v>46274.696574074071</v>
+        <v>46275.642025462963</v>
       </c>
       <c r="E34" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="F34" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G34">
-        <v>777313773</v>
+        <v>584572192</v>
       </c>
       <c r="H34" t="s">
         <v>122</v>
       </c>
-      <c r="I34" t="s">
-        <v>25</v>
+      <c r="I34">
+        <v>4118416</v>
       </c>
       <c r="J34" t="s">
+        <v>19</v>
+      </c>
+      <c r="K34" t="s">
+        <v>20</v>
+      </c>
+      <c r="L34" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34" t="s">
         <v>123</v>
       </c>
-      <c r="K34" t="s">
-        <v>119</v>
-      </c>
-      <c r="L34" t="s">
-        <v>55</v>
-      </c>
-      <c r="M34" t="s">
-        <v>22</v>
-      </c>
       <c r="N34" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O34" t="s">
         <v>25</v>
       </c>
-      <c r="P34" t="s">
-        <v>25</v>
+      <c r="P34" s="1">
+        <v>3000000</v>
       </c>
       <c r="Q34" t="s">
         <v>124</v>
@@ -2986,46 +2986,46 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>68233792</v>
+        <v>68272822</v>
       </c>
       <c r="B35" s="2">
-        <v>46246.680034722223</v>
+        <v>46247.469826388886</v>
       </c>
       <c r="C35">
-        <v>69930336</v>
+        <v>70595281</v>
       </c>
       <c r="D35" s="2">
-        <v>46275.644270833334</v>
+        <v>46286.554444444446</v>
       </c>
       <c r="E35" t="s">
-        <v>98</v>
+        <v>240</v>
       </c>
       <c r="F35" t="s">
         <v>125</v>
       </c>
       <c r="G35">
-        <v>584572192</v>
+        <v>709837321</v>
       </c>
       <c r="H35" t="s">
         <v>126</v>
       </c>
-      <c r="I35">
-        <v>4118436</v>
+      <c r="I35" t="s">
+        <v>25</v>
       </c>
       <c r="J35" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K35" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L35" t="s">
         <v>21</v>
       </c>
       <c r="M35" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="N35" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O35" t="s">
         <v>25</v>
@@ -3034,51 +3034,51 @@
         <v>25</v>
       </c>
       <c r="Q35" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>68233824</v>
+        <v>68272847</v>
       </c>
       <c r="B36" s="2">
-        <v>46246.680150462962</v>
+        <v>46247.469918981478</v>
       </c>
       <c r="C36">
-        <v>69930019</v>
+        <v>70584723</v>
       </c>
       <c r="D36" s="2">
-        <v>46275.642025462963</v>
+        <v>46286.504074074073</v>
       </c>
       <c r="E36" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="F36" t="s">
         <v>125</v>
       </c>
       <c r="G36">
-        <v>584572192</v>
+        <v>709837321</v>
       </c>
       <c r="H36" t="s">
-        <v>130</v>
-      </c>
-      <c r="I36">
-        <v>4118416</v>
+        <v>126</v>
+      </c>
+      <c r="I36" t="s">
+        <v>25</v>
       </c>
       <c r="J36" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K36" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="L36" t="s">
         <v>21</v>
       </c>
       <c r="M36" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="N36" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O36" t="s">
         <v>25</v>
@@ -3087,33 +3087,33 @@
         <v>3000000</v>
       </c>
       <c r="Q36" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>68272822</v>
+        <v>68294412</v>
       </c>
       <c r="B37" s="2">
-        <v>46247.469826388886</v>
+        <v>46247.620196759257</v>
       </c>
       <c r="C37">
-        <v>70238824</v>
+        <v>69571885</v>
       </c>
       <c r="D37" s="2">
-        <v>46281.385949074072</v>
+        <v>46269.49386574074</v>
       </c>
       <c r="E37" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="F37" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G37">
-        <v>709837321</v>
+        <v>2722522830</v>
       </c>
       <c r="H37" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I37" t="s">
         <v>25</v>
@@ -3122,13 +3122,13 @@
         <v>29</v>
       </c>
       <c r="K37" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="L37" t="s">
         <v>21</v>
       </c>
       <c r="M37" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="N37" t="s">
         <v>23</v>
@@ -3136,102 +3136,102 @@
       <c r="O37" t="s">
         <v>25</v>
       </c>
-      <c r="P37" t="s">
-        <v>25</v>
+      <c r="P37" s="1">
+        <v>7627200</v>
       </c>
       <c r="Q37" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>68272847</v>
+        <v>68362685</v>
       </c>
       <c r="B38" s="2">
-        <v>46247.469918981478</v>
+        <v>46248.453298611108</v>
       </c>
       <c r="C38">
-        <v>70402261</v>
+        <v>70210956</v>
       </c>
       <c r="D38" s="2">
-        <v>46283.447430555556</v>
+        <v>46280.698159722226</v>
       </c>
       <c r="E38" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G38">
-        <v>709837321</v>
+        <v>747708112</v>
       </c>
       <c r="H38" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="I38" t="s">
         <v>25</v>
       </c>
       <c r="J38" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="K38" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L38" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="M38" t="s">
-        <v>112</v>
+        <v>22</v>
       </c>
       <c r="N38" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O38" t="s">
         <v>25</v>
       </c>
-      <c r="P38" s="1">
-        <v>3000000</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>136</v>
+      <c r="P38" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q38">
+        <v>2722580515</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>68294412</v>
+        <v>68626233</v>
       </c>
       <c r="B39" s="2">
-        <v>46247.620196759257</v>
+        <v>46252.707268518519</v>
       </c>
       <c r="C39">
-        <v>69571885</v>
+        <v>69749985</v>
       </c>
       <c r="D39" s="2">
-        <v>46269.49386574074</v>
+        <v>46272.70652777778</v>
       </c>
       <c r="E39" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F39" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G39">
-        <v>2722522830</v>
+        <v>708223012</v>
       </c>
       <c r="H39" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I39" t="s">
         <v>25</v>
       </c>
       <c r="J39" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K39" t="s">
         <v>20</v>
       </c>
       <c r="L39" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M39" t="s">
         <v>22</v>
@@ -3243,104 +3243,104 @@
         <v>25</v>
       </c>
       <c r="P39" s="1">
-        <v>7627200</v>
+        <v>165000</v>
       </c>
       <c r="Q39" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>68362685</v>
+        <v>68677657</v>
       </c>
       <c r="B40" s="2">
-        <v>46248.453298611108</v>
+        <v>46253.601203703707</v>
       </c>
       <c r="C40">
-        <v>70210956</v>
+        <v>70344463</v>
       </c>
       <c r="D40" s="2">
-        <v>46280.698159722226</v>
+        <v>46282.559386574074</v>
       </c>
       <c r="E40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F40" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G40">
-        <v>747708112</v>
+        <v>585636245</v>
       </c>
       <c r="H40" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="I40" t="s">
         <v>25</v>
       </c>
       <c r="J40" t="s">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="K40" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L40" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="M40" t="s">
         <v>22</v>
       </c>
       <c r="N40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O40" t="s">
         <v>25</v>
       </c>
-      <c r="P40" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q40">
-        <v>2722580515</v>
+      <c r="P40" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>68626233</v>
+        <v>68721345</v>
       </c>
       <c r="B41" s="2">
-        <v>46252.707268518519</v>
+        <v>46254.410821759258</v>
       </c>
       <c r="C41">
-        <v>69749985</v>
+        <v>70134949</v>
       </c>
       <c r="D41" s="2">
-        <v>46272.70652777778</v>
+        <v>46279.659259259257</v>
       </c>
       <c r="E41" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G41">
-        <v>708223012</v>
+        <v>708086669</v>
       </c>
       <c r="H41" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I41" t="s">
         <v>25</v>
       </c>
       <c r="J41" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K41" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="L41" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="M41" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="N41" t="s">
         <v>23</v>
@@ -3348,108 +3348,108 @@
       <c r="O41" t="s">
         <v>25</v>
       </c>
-      <c r="P41" s="1">
-        <v>165000</v>
+      <c r="P41" t="s">
+        <v>25</v>
       </c>
       <c r="Q41" t="s">
-        <v>30</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>68677657</v>
+        <v>68721353</v>
       </c>
       <c r="B42" s="2">
-        <v>46253.601203703707</v>
+        <v>46254.410868055558</v>
       </c>
       <c r="C42">
-        <v>70344463</v>
+        <v>70134897</v>
       </c>
       <c r="D42" s="2">
-        <v>46282.559386574074</v>
+        <v>46279.659039351849</v>
       </c>
       <c r="E42" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="F42" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G42">
-        <v>585636245</v>
+        <v>708086669</v>
       </c>
       <c r="H42" t="s">
-        <v>143</v>
-      </c>
-      <c r="I42" t="s">
-        <v>25</v>
+        <v>140</v>
+      </c>
+      <c r="I42">
+        <v>4120006</v>
       </c>
       <c r="J42" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="K42" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="L42" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="M42" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="N42" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O42" t="s">
         <v>25</v>
       </c>
       <c r="P42" s="1">
-        <v>1500000</v>
+        <v>5324000</v>
       </c>
       <c r="Q42" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>68721345</v>
+        <v>68724737</v>
       </c>
       <c r="B43" s="2">
-        <v>46254.410821759258</v>
+        <v>46254.44190972222</v>
       </c>
       <c r="C43">
-        <v>70134949</v>
+        <v>69991967</v>
       </c>
       <c r="D43" s="2">
-        <v>46279.659259259257</v>
+        <v>46276.627164351848</v>
       </c>
       <c r="E43" t="s">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="F43" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G43">
-        <v>708086669</v>
+        <v>748377555</v>
       </c>
       <c r="H43" t="s">
-        <v>146</v>
-      </c>
-      <c r="I43" t="s">
-        <v>25</v>
+        <v>143</v>
+      </c>
+      <c r="I43">
+        <v>4121206</v>
       </c>
       <c r="J43" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="L43" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M43" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="N43" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O43" t="s">
         <v>25</v>
@@ -3458,48 +3458,48 @@
         <v>25</v>
       </c>
       <c r="Q43" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>68721353</v>
+        <v>68810204</v>
       </c>
       <c r="B44" s="2">
-        <v>46254.410868055558</v>
+        <v>46255.651574074072</v>
       </c>
       <c r="C44">
-        <v>70134897</v>
+        <v>69566569</v>
       </c>
       <c r="D44" s="2">
-        <v>46279.659039351849</v>
+        <v>46269.450439814813</v>
       </c>
       <c r="E44" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="F44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G44">
-        <v>708086669</v>
+        <v>777453388</v>
       </c>
       <c r="H44" t="s">
-        <v>148</v>
-      </c>
-      <c r="I44">
-        <v>4120006</v>
+        <v>97</v>
+      </c>
+      <c r="I44" t="s">
+        <v>25</v>
       </c>
       <c r="J44" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="K44" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="L44" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="M44" t="s">
-        <v>112</v>
+        <v>22</v>
       </c>
       <c r="N44" t="s">
         <v>23</v>
@@ -3507,143 +3507,143 @@
       <c r="O44" t="s">
         <v>25</v>
       </c>
-      <c r="P44" s="1">
-        <v>5324000</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>149</v>
+      <c r="P44" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q44">
+        <v>2721712305</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>68724737</v>
+        <v>68981818</v>
       </c>
       <c r="B45" s="2">
-        <v>46254.44190972222</v>
+        <v>46258.805046296293</v>
       </c>
       <c r="C45">
-        <v>69991967</v>
+        <v>70403956</v>
       </c>
       <c r="D45" s="2">
-        <v>46276.627164351848</v>
+        <v>46283.459305555552</v>
       </c>
       <c r="E45" t="s">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="F45" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G45">
-        <v>748377555</v>
+        <v>707349695</v>
       </c>
       <c r="H45" t="s">
-        <v>151</v>
-      </c>
-      <c r="I45">
-        <v>4121206</v>
+        <v>133</v>
+      </c>
+      <c r="I45" t="s">
+        <v>25</v>
       </c>
       <c r="J45" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="K45" t="s">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="L45" t="s">
         <v>37</v>
       </c>
       <c r="M45" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="N45" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O45" t="s">
         <v>25</v>
       </c>
-      <c r="P45" t="s">
-        <v>25</v>
+      <c r="P45">
+        <v>0</v>
       </c>
       <c r="Q45" t="s">
-        <v>25</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>68810204</v>
+        <v>68982046</v>
       </c>
       <c r="B46" s="2">
-        <v>46255.651574074072</v>
+        <v>46258.809212962966</v>
       </c>
       <c r="C46">
-        <v>69566569</v>
+        <v>70099229</v>
       </c>
       <c r="D46" s="2">
-        <v>46269.450439814813</v>
+        <v>46279.373148148145</v>
       </c>
       <c r="E46" t="s">
-        <v>155</v>
+        <v>66</v>
       </c>
       <c r="F46" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G46">
-        <v>777453388</v>
+        <v>707349695</v>
       </c>
       <c r="H46" t="s">
-        <v>101</v>
+        <v>150</v>
       </c>
       <c r="I46" t="s">
         <v>25</v>
       </c>
       <c r="J46" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="K46" t="s">
+        <v>20</v>
+      </c>
+      <c r="L46" t="s">
+        <v>37</v>
+      </c>
+      <c r="M46" t="s">
+        <v>41</v>
+      </c>
+      <c r="N46" t="s">
         <v>54</v>
       </c>
-      <c r="L46" t="s">
-        <v>55</v>
-      </c>
-      <c r="M46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N46" t="s">
-        <v>23</v>
-      </c>
       <c r="O46" t="s">
         <v>25</v>
       </c>
-      <c r="P46" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q46">
-        <v>2721712305</v>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>68981818</v>
+        <v>68982246</v>
       </c>
       <c r="B47" s="2">
-        <v>46258.805046296293</v>
+        <v>46258.813020833331</v>
       </c>
       <c r="C47">
-        <v>70403956</v>
+        <v>69748280</v>
       </c>
       <c r="D47" s="2">
-        <v>46283.459305555552</v>
+        <v>46272.695138888892</v>
       </c>
       <c r="E47" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F47" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="G47">
         <v>707349695</v>
       </c>
       <c r="H47" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="I47" t="s">
         <v>25</v>
@@ -3670,48 +3670,48 @@
         <v>0</v>
       </c>
       <c r="Q47" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>68982046</v>
+        <v>69043021</v>
       </c>
       <c r="B48" s="2">
-        <v>46258.809212962966</v>
+        <v>46260.4452662037</v>
       </c>
       <c r="C48">
-        <v>70099229</v>
+        <v>69874129</v>
       </c>
       <c r="D48" s="2">
-        <v>46279.373148148145</v>
+        <v>46274.694849537038</v>
       </c>
       <c r="E48" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F48" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G48">
-        <v>707349695</v>
+        <v>574382964</v>
       </c>
       <c r="H48" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="I48" t="s">
         <v>25</v>
       </c>
       <c r="J48" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K48" t="s">
         <v>20</v>
       </c>
       <c r="L48" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="M48" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="N48" t="s">
         <v>23</v>
@@ -3719,52 +3719,52 @@
       <c r="O48" t="s">
         <v>25</v>
       </c>
-      <c r="P48">
-        <v>0</v>
+      <c r="P48" s="1">
+        <v>1600000</v>
       </c>
       <c r="Q48" t="s">
-        <v>159</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>68982246</v>
+        <v>69111522</v>
       </c>
       <c r="B49" s="2">
-        <v>46258.813020833331</v>
+        <v>46261.479409722226</v>
       </c>
       <c r="C49">
-        <v>69748280</v>
+        <v>69751700</v>
       </c>
       <c r="D49" s="2">
-        <v>46272.695138888892</v>
+        <v>46272.719456018516</v>
       </c>
       <c r="E49" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F49" t="s">
+        <v>155</v>
+      </c>
+      <c r="G49">
+        <v>507071129</v>
+      </c>
+      <c r="H49" t="s">
         <v>156</v>
       </c>
-      <c r="G49">
-        <v>707349695</v>
-      </c>
-      <c r="H49" t="s">
-        <v>160</v>
-      </c>
       <c r="I49" t="s">
         <v>25</v>
       </c>
       <c r="J49" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K49" t="s">
         <v>20</v>
       </c>
       <c r="L49" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="M49" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="N49" t="s">
         <v>23</v>
@@ -3772,37 +3772,37 @@
       <c r="O49" t="s">
         <v>25</v>
       </c>
-      <c r="P49">
-        <v>0</v>
+      <c r="P49" s="1">
+        <v>4557729</v>
       </c>
       <c r="Q49" t="s">
-        <v>161</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>69043021</v>
+        <v>69116821</v>
       </c>
       <c r="B50" s="2">
-        <v>46260.4452662037</v>
+        <v>46261.519444444442</v>
       </c>
       <c r="C50">
-        <v>69874129</v>
+        <v>69641140</v>
       </c>
       <c r="D50" s="2">
-        <v>46274.694849537038</v>
+        <v>46270.549120370371</v>
       </c>
       <c r="E50" t="s">
         <v>47</v>
       </c>
       <c r="F50" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G50">
-        <v>574382964</v>
+        <v>711255757</v>
       </c>
       <c r="H50" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="I50" t="s">
         <v>25</v>
@@ -3825,37 +3825,37 @@
       <c r="O50" t="s">
         <v>25</v>
       </c>
-      <c r="P50" s="1">
-        <v>1600000</v>
+      <c r="P50">
+        <v>0</v>
       </c>
       <c r="Q50" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>69111522</v>
+        <v>69131271</v>
       </c>
       <c r="B51" s="2">
-        <v>46261.479409722226</v>
+        <v>46261.635115740741</v>
       </c>
       <c r="C51">
-        <v>69751700</v>
+        <v>69332398</v>
       </c>
       <c r="D51" s="2">
-        <v>46272.719456018516</v>
+        <v>46265.606851851851</v>
       </c>
       <c r="E51" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F51" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G51">
-        <v>507071129</v>
+        <v>716207520</v>
       </c>
       <c r="H51" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I51" t="s">
         <v>25</v>
@@ -3864,7 +3864,7 @@
         <v>29</v>
       </c>
       <c r="K51" t="s">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="L51" t="s">
         <v>21</v>
@@ -3873,42 +3873,42 @@
         <v>22</v>
       </c>
       <c r="N51" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O51" t="s">
         <v>25</v>
       </c>
       <c r="P51" s="1">
-        <v>4557729</v>
+        <v>5000000</v>
       </c>
       <c r="Q51" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>69116821</v>
+        <v>69133094</v>
       </c>
       <c r="B52" s="2">
-        <v>46261.519444444442</v>
+        <v>46261.648576388892</v>
       </c>
       <c r="C52">
-        <v>69641140</v>
+        <v>70172509</v>
       </c>
       <c r="D52" s="2">
-        <v>46270.549120370371</v>
+        <v>46280.40834490741</v>
       </c>
       <c r="E52" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="F52" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G52">
-        <v>711255757</v>
+        <v>716207520</v>
       </c>
       <c r="H52" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I52" t="s">
         <v>25</v>
@@ -3917,7 +3917,7 @@
         <v>29</v>
       </c>
       <c r="K52" t="s">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="L52" t="s">
         <v>21</v>
@@ -3926,42 +3926,42 @@
         <v>22</v>
       </c>
       <c r="N52" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O52" t="s">
         <v>25</v>
       </c>
-      <c r="P52">
-        <v>0</v>
+      <c r="P52" s="1">
+        <v>5000000</v>
       </c>
       <c r="Q52" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>69131271</v>
+        <v>69135728</v>
       </c>
       <c r="B53" s="2">
-        <v>46261.635115740741</v>
+        <v>46261.667939814812</v>
       </c>
       <c r="C53">
-        <v>69332398</v>
+        <v>69641076</v>
       </c>
       <c r="D53" s="2">
-        <v>46265.606851851851</v>
+        <v>46270.548171296294</v>
       </c>
       <c r="E53" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="F53" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="G53">
-        <v>716207520</v>
+        <v>711255757</v>
       </c>
       <c r="H53" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I53" t="s">
         <v>25</v>
@@ -3970,7 +3970,7 @@
         <v>29</v>
       </c>
       <c r="K53" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="L53" t="s">
         <v>21</v>
@@ -3979,42 +3979,42 @@
         <v>22</v>
       </c>
       <c r="N53" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O53" t="s">
         <v>25</v>
       </c>
-      <c r="P53" s="1">
-        <v>5000000</v>
+      <c r="P53">
+        <v>0</v>
       </c>
       <c r="Q53" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>69133094</v>
+        <v>69173063</v>
       </c>
       <c r="B54" s="2">
-        <v>46261.648576388892</v>
+        <v>46262.440787037034</v>
       </c>
       <c r="C54">
-        <v>70172509</v>
+        <v>70278496</v>
       </c>
       <c r="D54" s="2">
-        <v>46280.40834490741</v>
+        <v>46281.688391203701</v>
       </c>
       <c r="E54" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="F54" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G54">
-        <v>716207520</v>
+        <v>707093185</v>
       </c>
       <c r="H54" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I54" t="s">
         <v>25</v>
@@ -4023,7 +4023,7 @@
         <v>29</v>
       </c>
       <c r="K54" t="s">
-        <v>169</v>
+        <v>105</v>
       </c>
       <c r="L54" t="s">
         <v>21</v>
@@ -4032,42 +4032,42 @@
         <v>22</v>
       </c>
       <c r="N54" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O54" t="s">
         <v>25</v>
       </c>
       <c r="P54" s="1">
-        <v>5000000</v>
+        <v>484889</v>
       </c>
       <c r="Q54" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>69135728</v>
+        <v>69372201</v>
       </c>
       <c r="B55" s="2">
-        <v>46261.667939814812</v>
+        <v>46266.366759259261</v>
       </c>
       <c r="C55">
-        <v>69641076</v>
+        <v>69967282</v>
       </c>
       <c r="D55" s="2">
-        <v>46270.548171296294</v>
+        <v>46276.437754629631</v>
       </c>
       <c r="E55" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="F55" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G55">
-        <v>711255757</v>
+        <v>767094330</v>
       </c>
       <c r="H55" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I55" t="s">
         <v>25</v>
@@ -4076,51 +4076,51 @@
         <v>29</v>
       </c>
       <c r="K55" t="s">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="L55" t="s">
         <v>21</v>
       </c>
       <c r="M55" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="N55" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O55" t="s">
         <v>25</v>
       </c>
-      <c r="P55">
-        <v>0</v>
+      <c r="P55" s="1">
+        <v>1386000</v>
       </c>
       <c r="Q55" t="s">
-        <v>82</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>69173063</v>
+        <v>69379141</v>
       </c>
       <c r="B56" s="2">
-        <v>46262.440787037034</v>
+        <v>46266.434988425928</v>
       </c>
       <c r="C56">
-        <v>70278496</v>
+        <v>69774019</v>
       </c>
       <c r="D56" s="2">
-        <v>46281.688391203701</v>
+        <v>46273.399398148147</v>
       </c>
       <c r="E56" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="F56" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G56">
-        <v>707093185</v>
+        <v>545452401</v>
       </c>
       <c r="H56" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I56" t="s">
         <v>25</v>
@@ -4129,7 +4129,7 @@
         <v>29</v>
       </c>
       <c r="K56" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="L56" t="s">
         <v>21</v>
@@ -4138,42 +4138,42 @@
         <v>22</v>
       </c>
       <c r="N56" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O56" t="s">
         <v>25</v>
       </c>
       <c r="P56" s="1">
-        <v>484889</v>
+        <v>2800000</v>
       </c>
       <c r="Q56" t="s">
-        <v>176</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>69372201</v>
+        <v>69434883</v>
       </c>
       <c r="B57" s="2">
-        <v>46266.366759259261</v>
+        <v>46267.335902777777</v>
       </c>
       <c r="C57">
-        <v>69967282</v>
+        <v>70586972</v>
       </c>
       <c r="D57" s="2">
-        <v>46276.437754629631</v>
+        <v>46286.515011574076</v>
       </c>
       <c r="E57" t="s">
-        <v>75</v>
+        <v>239</v>
       </c>
       <c r="F57" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G57">
-        <v>767094330</v>
+        <v>778197272</v>
       </c>
       <c r="H57" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I57" t="s">
         <v>25</v>
@@ -4182,104 +4182,104 @@
         <v>29</v>
       </c>
       <c r="K57" t="s">
-        <v>169</v>
+        <v>105</v>
       </c>
       <c r="L57" t="s">
         <v>21</v>
       </c>
       <c r="M57" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="N57" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O57" t="s">
         <v>25</v>
       </c>
       <c r="P57" s="1">
-        <v>1386000</v>
+        <v>1480307</v>
       </c>
       <c r="Q57" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>69379141</v>
+        <v>69451554</v>
       </c>
       <c r="B58" s="2">
-        <v>46266.434988425928</v>
+        <v>46267.503969907404</v>
       </c>
       <c r="C58">
-        <v>69774019</v>
+        <v>70599583</v>
       </c>
       <c r="D58" s="2">
-        <v>46273.399398148147</v>
+        <v>46286.575902777775</v>
       </c>
       <c r="E58" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F58" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="G58">
-        <v>545452401</v>
+        <v>759000860</v>
       </c>
       <c r="H58" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I58" t="s">
         <v>25</v>
       </c>
       <c r="J58" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="K58" t="s">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="L58" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="M58" t="s">
         <v>22</v>
       </c>
       <c r="N58" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O58" t="s">
         <v>25</v>
       </c>
-      <c r="P58" s="1">
-        <v>2800000</v>
+      <c r="P58" t="s">
+        <v>25</v>
       </c>
       <c r="Q58" t="s">
-        <v>25</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>69434883</v>
+        <v>69529704</v>
       </c>
       <c r="B59" s="2">
-        <v>46267.335902777777</v>
+        <v>46268.647164351853</v>
       </c>
       <c r="C59">
-        <v>70406472</v>
+        <v>70581776</v>
       </c>
       <c r="D59" s="2">
-        <v>46283.476770833331</v>
+        <v>46286.491249999999</v>
       </c>
       <c r="E59" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="F59" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G59">
-        <v>778197272</v>
+        <v>506375785</v>
       </c>
       <c r="H59" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I59" t="s">
         <v>25</v>
@@ -4303,55 +4303,55 @@
         <v>25</v>
       </c>
       <c r="P59" s="1">
-        <v>1480307</v>
+        <v>1000000</v>
       </c>
       <c r="Q59" t="s">
-        <v>30</v>
+        <v>180</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>69451554</v>
+        <v>69530589</v>
       </c>
       <c r="B60" s="2">
-        <v>46267.503969907404</v>
+        <v>46268.654768518521</v>
       </c>
       <c r="C60">
-        <v>70401963</v>
+        <v>70587082</v>
       </c>
       <c r="D60" s="2">
-        <v>46283.445416666669</v>
+        <v>46286.515509259261</v>
       </c>
       <c r="E60" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="F60" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="G60">
-        <v>759000860</v>
+        <v>778197272</v>
       </c>
       <c r="H60" t="s">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="I60" t="s">
         <v>25</v>
       </c>
       <c r="J60" t="s">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="K60" t="s">
+        <v>52</v>
+      </c>
+      <c r="L60" t="s">
+        <v>53</v>
+      </c>
+      <c r="M60" t="s">
+        <v>22</v>
+      </c>
+      <c r="N60" t="s">
         <v>54</v>
       </c>
-      <c r="L60" t="s">
-        <v>55</v>
-      </c>
-      <c r="M60" t="s">
-        <v>22</v>
-      </c>
-      <c r="N60" t="s">
-        <v>56</v>
-      </c>
       <c r="O60" t="s">
         <v>25</v>
       </c>
@@ -4359,45 +4359,45 @@
         <v>25</v>
       </c>
       <c r="Q60" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>69529704</v>
+        <v>69576604</v>
       </c>
       <c r="B61" s="2">
-        <v>46268.647164351853</v>
+        <v>46269.533125000002</v>
       </c>
       <c r="C61">
-        <v>70416877</v>
+        <v>70563619</v>
       </c>
       <c r="D61" s="2">
-        <v>46283.558993055558</v>
+        <v>46286.037708333337</v>
       </c>
       <c r="E61" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F61" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G61">
-        <v>506375785</v>
+        <v>707965801</v>
       </c>
       <c r="H61" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I61" t="s">
         <v>25</v>
       </c>
       <c r="J61" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="K61" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="L61" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="M61" t="s">
         <v>22</v>
@@ -4408,49 +4408,49 @@
       <c r="O61" t="s">
         <v>25</v>
       </c>
-      <c r="P61" s="1">
-        <v>1000000</v>
+      <c r="P61" t="s">
+        <v>25</v>
       </c>
       <c r="Q61" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>69530589</v>
+        <v>69610261</v>
       </c>
       <c r="B62" s="2">
-        <v>46268.654768518521</v>
+        <v>46269.880844907406</v>
       </c>
       <c r="C62">
-        <v>70405096</v>
+        <v>69830754</v>
       </c>
       <c r="D62" s="2">
-        <v>46283.466817129629</v>
+        <v>46274.050104166665</v>
       </c>
       <c r="E62" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="F62" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G62">
-        <v>778197272</v>
+        <v>757911775</v>
       </c>
       <c r="H62" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="I62" t="s">
         <v>25</v>
       </c>
       <c r="J62" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="K62" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="L62" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="M62" t="s">
         <v>22</v>
@@ -4461,49 +4461,49 @@
       <c r="O62" t="s">
         <v>25</v>
       </c>
-      <c r="P62" t="s">
-        <v>25</v>
+      <c r="P62" s="1">
+        <v>2372508</v>
       </c>
       <c r="Q62" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>69576604</v>
+        <v>69636615</v>
       </c>
       <c r="B63" s="2">
-        <v>46269.533125000002</v>
+        <v>46270.500671296293</v>
       </c>
       <c r="C63">
-        <v>69779302</v>
+        <v>69830744</v>
       </c>
       <c r="D63" s="2">
-        <v>46273.44667824074</v>
+        <v>46274.0469212963</v>
       </c>
       <c r="E63" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="F63" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G63">
-        <v>707965801</v>
+        <v>504033918</v>
       </c>
       <c r="H63" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I63" t="s">
         <v>25</v>
       </c>
       <c r="J63" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="K63" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="L63" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="M63" t="s">
         <v>22</v>
@@ -4514,37 +4514,37 @@
       <c r="O63" t="s">
         <v>25</v>
       </c>
-      <c r="P63" t="s">
-        <v>25</v>
+      <c r="P63" s="1">
+        <v>4000000</v>
       </c>
       <c r="Q63" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>69610261</v>
+        <v>69638056</v>
       </c>
       <c r="B64" s="2">
-        <v>46269.880844907406</v>
+        <v>46270.517337962963</v>
       </c>
       <c r="C64">
-        <v>69830754</v>
+        <v>69830743</v>
       </c>
       <c r="D64" s="2">
-        <v>46274.050104166665</v>
+        <v>46274.046423611115</v>
       </c>
       <c r="E64" t="s">
         <v>47</v>
       </c>
       <c r="F64" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="G64">
-        <v>757911775</v>
+        <v>709574114</v>
       </c>
       <c r="H64" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="I64" t="s">
         <v>25</v>
@@ -4568,51 +4568,51 @@
         <v>25</v>
       </c>
       <c r="P64" s="1">
-        <v>2372508</v>
+        <v>1445307</v>
       </c>
       <c r="Q64" t="s">
-        <v>25</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>69636615</v>
+        <v>69639820</v>
       </c>
       <c r="B65" s="2">
-        <v>46270.500671296293</v>
+        <v>46270.535324074073</v>
       </c>
       <c r="C65">
-        <v>69830744</v>
+        <v>69830745</v>
       </c>
       <c r="D65" s="2">
-        <v>46274.0469212963</v>
+        <v>46274.047407407408</v>
       </c>
       <c r="E65" t="s">
         <v>47</v>
       </c>
       <c r="F65" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G65">
-        <v>504033918</v>
+        <v>767791237</v>
       </c>
       <c r="H65" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="I65" t="s">
         <v>25</v>
       </c>
       <c r="J65" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K65" t="s">
         <v>20</v>
       </c>
       <c r="L65" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="M65" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="N65" t="s">
         <v>23</v>
@@ -4620,49 +4620,49 @@
       <c r="O65" t="s">
         <v>25</v>
       </c>
-      <c r="P65" s="1">
-        <v>4000000</v>
+      <c r="P65">
+        <v>0</v>
       </c>
       <c r="Q65" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>69638056</v>
+        <v>69641187</v>
       </c>
       <c r="B66" s="2">
-        <v>46270.517337962963</v>
+        <v>46270.549791666665</v>
       </c>
       <c r="C66">
-        <v>69830743</v>
+        <v>69830749</v>
       </c>
       <c r="D66" s="2">
-        <v>46274.046423611115</v>
+        <v>46274.048032407409</v>
       </c>
       <c r="E66" t="s">
         <v>47</v>
       </c>
       <c r="F66" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G66">
-        <v>709574114</v>
+        <v>160128782</v>
       </c>
       <c r="H66" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I66" t="s">
         <v>25</v>
       </c>
       <c r="J66" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K66" t="s">
         <v>20</v>
       </c>
       <c r="L66" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M66" t="s">
         <v>22</v>
@@ -4674,36 +4674,36 @@
         <v>25</v>
       </c>
       <c r="P66" s="1">
-        <v>1445307</v>
+        <v>800000</v>
       </c>
       <c r="Q66" t="s">
-        <v>161</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>69639820</v>
+        <v>69642851</v>
       </c>
       <c r="B67" s="2">
-        <v>46270.535324074073</v>
+        <v>46270.56858796296</v>
       </c>
       <c r="C67">
-        <v>69830745</v>
+        <v>69830752</v>
       </c>
       <c r="D67" s="2">
-        <v>46274.047407407408</v>
+        <v>46274.048888888887</v>
       </c>
       <c r="E67" t="s">
         <v>47</v>
       </c>
       <c r="F67" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="G67">
-        <v>767791237</v>
+        <v>707234610</v>
       </c>
       <c r="H67" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I67" t="s">
         <v>25</v>
@@ -4718,7 +4718,7 @@
         <v>21</v>
       </c>
       <c r="M67" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="N67" t="s">
         <v>23</v>
@@ -4726,37 +4726,37 @@
       <c r="O67" t="s">
         <v>25</v>
       </c>
-      <c r="P67">
-        <v>0</v>
+      <c r="P67" s="1">
+        <v>3070672</v>
       </c>
       <c r="Q67" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>69641187</v>
+        <v>69644355</v>
       </c>
       <c r="B68" s="2">
-        <v>46270.549791666665</v>
+        <v>46270.58625</v>
       </c>
       <c r="C68">
-        <v>69830749</v>
+        <v>69830751</v>
       </c>
       <c r="D68" s="2">
-        <v>46274.048032407409</v>
+        <v>46274.048437500001</v>
       </c>
       <c r="E68" t="s">
         <v>47</v>
       </c>
       <c r="F68" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G68">
-        <v>160128782</v>
+        <v>707984429</v>
       </c>
       <c r="H68" t="s">
-        <v>200</v>
+        <v>28</v>
       </c>
       <c r="I68" t="s">
         <v>25</v>
@@ -4780,48 +4780,48 @@
         <v>25</v>
       </c>
       <c r="P68" s="1">
-        <v>800000</v>
+        <v>2984038</v>
       </c>
       <c r="Q68" t="s">
-        <v>30</v>
+        <v>153</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>69642851</v>
+        <v>69645417</v>
       </c>
       <c r="B69" s="2">
-        <v>46270.56858796296</v>
+        <v>46270.599270833336</v>
       </c>
       <c r="C69">
-        <v>69830752</v>
+        <v>69830736</v>
       </c>
       <c r="D69" s="2">
-        <v>46274.048888888887</v>
+        <v>46274.043182870373</v>
       </c>
       <c r="E69" t="s">
         <v>47</v>
       </c>
       <c r="F69" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G69">
-        <v>707234610</v>
+        <v>707722441</v>
       </c>
       <c r="H69" t="s">
-        <v>202</v>
+        <v>28</v>
       </c>
       <c r="I69" t="s">
         <v>25</v>
       </c>
       <c r="J69" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K69" t="s">
         <v>20</v>
       </c>
       <c r="L69" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M69" t="s">
         <v>22</v>
@@ -4833,48 +4833,48 @@
         <v>25</v>
       </c>
       <c r="P69" s="1">
-        <v>3070672</v>
+        <v>1513624</v>
       </c>
       <c r="Q69" t="s">
-        <v>30</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>69644355</v>
+        <v>69646685</v>
       </c>
       <c r="B70" s="2">
-        <v>46270.58625</v>
+        <v>46270.614340277774</v>
       </c>
       <c r="C70">
-        <v>69830751</v>
+        <v>69830755</v>
       </c>
       <c r="D70" s="2">
-        <v>46274.048437500001</v>
+        <v>46274.050486111111</v>
       </c>
       <c r="E70" t="s">
         <v>47</v>
       </c>
       <c r="F70" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G70">
-        <v>707984429</v>
+        <v>711458931</v>
       </c>
       <c r="H70" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="I70" t="s">
         <v>25</v>
       </c>
       <c r="J70" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K70" t="s">
         <v>20</v>
       </c>
       <c r="L70" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="M70" t="s">
         <v>22</v>
@@ -4886,42 +4886,42 @@
         <v>25</v>
       </c>
       <c r="P70" s="1">
-        <v>2984038</v>
+        <v>1000000</v>
       </c>
       <c r="Q70" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>69645417</v>
+        <v>69710858</v>
       </c>
       <c r="B71" s="2">
-        <v>46270.599270833336</v>
+        <v>46272.419942129629</v>
       </c>
       <c r="C71">
-        <v>69830736</v>
+        <v>70215767</v>
       </c>
       <c r="D71" s="2">
-        <v>46274.043182870373</v>
+        <v>46280.735092592593</v>
       </c>
       <c r="E71" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="F71" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G71">
-        <v>707722441</v>
+        <v>194925700</v>
       </c>
       <c r="H71" t="s">
-        <v>28</v>
+        <v>199</v>
       </c>
       <c r="I71" t="s">
         <v>25</v>
       </c>
       <c r="J71" t="s">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="K71" t="s">
         <v>20</v>
@@ -4933,54 +4933,54 @@
         <v>22</v>
       </c>
       <c r="N71" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O71" t="s">
         <v>25</v>
       </c>
-      <c r="P71" s="1">
-        <v>1513624</v>
+      <c r="P71" t="s">
+        <v>25</v>
       </c>
       <c r="Q71" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>69646685</v>
+        <v>69712075</v>
       </c>
       <c r="B72" s="2">
-        <v>46270.614340277774</v>
+        <v>46272.429722222223</v>
       </c>
       <c r="C72">
-        <v>69830755</v>
+        <v>70367574</v>
       </c>
       <c r="D72" s="2">
-        <v>46274.050486111111</v>
+        <v>46282.726053240738</v>
       </c>
       <c r="E72" t="s">
-        <v>47</v>
+        <v>203</v>
       </c>
       <c r="F72" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G72">
-        <v>711458931</v>
+        <v>194925700</v>
       </c>
       <c r="H72" t="s">
-        <v>141</v>
+        <v>201</v>
       </c>
       <c r="I72" t="s">
         <v>25</v>
       </c>
       <c r="J72" t="s">
-        <v>29</v>
+        <v>200</v>
       </c>
       <c r="K72" t="s">
         <v>20</v>
       </c>
       <c r="L72" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M72" t="s">
         <v>22</v>
@@ -4991,102 +4991,102 @@
       <c r="O72" t="s">
         <v>25</v>
       </c>
-      <c r="P72" s="1">
-        <v>1000000</v>
+      <c r="P72" t="s">
+        <v>25</v>
       </c>
       <c r="Q72" t="s">
-        <v>33</v>
+        <v>202</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>69710858</v>
+        <v>69714119</v>
       </c>
       <c r="B73" s="2">
-        <v>46272.419942129629</v>
+        <v>46272.447245370371</v>
       </c>
       <c r="C73">
-        <v>70215767</v>
+        <v>69830741</v>
       </c>
       <c r="D73" s="2">
-        <v>46280.735092592593</v>
+        <v>46274.045428240737</v>
       </c>
       <c r="E73" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="F73" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G73">
-        <v>194925700</v>
+        <v>720631500</v>
       </c>
       <c r="H73" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I73" t="s">
         <v>25</v>
       </c>
       <c r="J73" t="s">
-        <v>208</v>
+        <v>29</v>
       </c>
       <c r="K73" t="s">
         <v>20</v>
       </c>
       <c r="L73" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="M73" t="s">
         <v>22</v>
       </c>
       <c r="N73" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O73" t="s">
         <v>25</v>
       </c>
-      <c r="P73" t="s">
-        <v>25</v>
+      <c r="P73" s="1">
+        <v>4406780</v>
       </c>
       <c r="Q73" t="s">
-        <v>157</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>69712075</v>
+        <v>69749460</v>
       </c>
       <c r="B74" s="2">
-        <v>46272.429722222223</v>
+        <v>46272.702685185184</v>
       </c>
       <c r="C74">
-        <v>70367574</v>
+        <v>69830730</v>
       </c>
       <c r="D74" s="2">
-        <v>46282.726053240738</v>
+        <v>46274.042708333334</v>
       </c>
       <c r="E74" t="s">
-        <v>211</v>
+        <v>47</v>
       </c>
       <c r="F74" t="s">
         <v>206</v>
       </c>
       <c r="G74">
-        <v>194925700</v>
+        <v>595999281</v>
       </c>
       <c r="H74" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I74" t="s">
         <v>25</v>
       </c>
       <c r="J74" t="s">
-        <v>208</v>
+        <v>115</v>
       </c>
       <c r="K74" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="L74" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="M74" t="s">
         <v>22</v>
@@ -5101,33 +5101,33 @@
         <v>25</v>
       </c>
       <c r="Q74" t="s">
-        <v>210</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>69714119</v>
+        <v>69790474</v>
       </c>
       <c r="B75" s="2">
-        <v>46272.447245370371</v>
+        <v>46273.525081018517</v>
       </c>
       <c r="C75">
-        <v>69830741</v>
+        <v>70407147</v>
       </c>
       <c r="D75" s="2">
-        <v>46274.045428240737</v>
+        <v>46283.481145833335</v>
       </c>
       <c r="E75" t="s">
-        <v>47</v>
+        <v>210</v>
       </c>
       <c r="F75" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G75">
-        <v>720631500</v>
+        <v>707723902</v>
       </c>
       <c r="H75" t="s">
-        <v>213</v>
+        <v>111</v>
       </c>
       <c r="I75" t="s">
         <v>25</v>
@@ -5136,7 +5136,7 @@
         <v>29</v>
       </c>
       <c r="K75" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="L75" t="s">
         <v>21</v>
@@ -5151,48 +5151,48 @@
         <v>25</v>
       </c>
       <c r="P75" s="1">
-        <v>4406780</v>
+        <v>500000</v>
       </c>
       <c r="Q75" t="s">
-        <v>82</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>69749460</v>
+        <v>69805967</v>
       </c>
       <c r="B76" s="2">
-        <v>46272.702685185184</v>
+        <v>46273.647175925929</v>
       </c>
       <c r="C76">
-        <v>69830730</v>
+        <v>70563611</v>
       </c>
       <c r="D76" s="2">
-        <v>46274.042708333334</v>
+        <v>46286.036435185182</v>
       </c>
       <c r="E76" t="s">
         <v>47</v>
       </c>
       <c r="F76" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G76">
-        <v>595999281</v>
+        <v>748110202</v>
       </c>
       <c r="H76" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I76" t="s">
         <v>25</v>
       </c>
       <c r="J76" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="K76" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="L76" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="M76" t="s">
         <v>22</v>
@@ -5203,37 +5203,37 @@
       <c r="O76" t="s">
         <v>25</v>
       </c>
-      <c r="P76" t="s">
-        <v>25</v>
+      <c r="P76" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q76" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>69790474</v>
+        <v>69814197</v>
       </c>
       <c r="B77" s="2">
-        <v>46273.525081018517</v>
+        <v>46273.707986111112</v>
       </c>
       <c r="C77">
-        <v>70407147</v>
+        <v>70563610</v>
       </c>
       <c r="D77" s="2">
-        <v>46283.481145833335</v>
+        <v>46286.036111111112</v>
       </c>
       <c r="E77" t="s">
-        <v>218</v>
+        <v>47</v>
       </c>
       <c r="F77" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G77">
-        <v>707723902</v>
+        <v>707730380</v>
       </c>
       <c r="H77" t="s">
-        <v>118</v>
+        <v>214</v>
       </c>
       <c r="I77" t="s">
         <v>25</v>
@@ -5242,7 +5242,7 @@
         <v>29</v>
       </c>
       <c r="K77" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="L77" t="s">
         <v>21</v>
@@ -5257,48 +5257,48 @@
         <v>25</v>
       </c>
       <c r="P77" s="1">
-        <v>500000</v>
+        <v>957418</v>
       </c>
       <c r="Q77" t="s">
-        <v>217</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>69805967</v>
+        <v>69840573</v>
       </c>
       <c r="B78" s="2">
-        <v>46273.647175925929</v>
+        <v>46274.434444444443</v>
       </c>
       <c r="C78">
-        <v>70125169</v>
+        <v>70563638</v>
       </c>
       <c r="D78" s="2">
-        <v>46279.591909722221</v>
+        <v>46286.039918981478</v>
       </c>
       <c r="E78" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="F78" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G78">
-        <v>748110202</v>
+        <v>708504392</v>
       </c>
       <c r="H78" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I78" t="s">
         <v>25</v>
       </c>
       <c r="J78" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K78" t="s">
         <v>20</v>
       </c>
       <c r="L78" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M78" t="s">
         <v>22</v>
@@ -5310,48 +5310,48 @@
         <v>25</v>
       </c>
       <c r="P78" s="1">
-        <v>2000000</v>
+        <v>1862455</v>
       </c>
       <c r="Q78" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>69814197</v>
+        <v>69845984</v>
       </c>
       <c r="B79" s="2">
-        <v>46273.707986111112</v>
+        <v>46274.481273148151</v>
       </c>
       <c r="C79">
-        <v>70124747</v>
+        <v>70577097</v>
       </c>
       <c r="D79" s="2">
-        <v>46279.588090277779</v>
+        <v>46286.45921296296</v>
       </c>
       <c r="E79" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F79" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="G79">
         <v>707730380</v>
       </c>
       <c r="H79" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="I79" t="s">
         <v>25</v>
       </c>
       <c r="J79" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="K79" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="L79" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="M79" t="s">
         <v>22</v>
@@ -5362,49 +5362,49 @@
       <c r="O79" t="s">
         <v>25</v>
       </c>
-      <c r="P79" s="1">
-        <v>957418</v>
+      <c r="P79" t="s">
+        <v>25</v>
       </c>
       <c r="Q79" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>69840573</v>
+        <v>69929747</v>
       </c>
       <c r="B80" s="2">
-        <v>46274.434444444443</v>
+        <v>46275.640439814815</v>
       </c>
       <c r="C80">
-        <v>70215050</v>
+        <v>70576392</v>
       </c>
       <c r="D80" s="2">
-        <v>46280.728518518517</v>
+        <v>46286.453136574077</v>
       </c>
       <c r="E80" t="s">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="F80" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G80">
-        <v>708504392</v>
+        <v>709090251</v>
       </c>
       <c r="H80" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="I80" t="s">
         <v>25</v>
       </c>
       <c r="J80" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K80" t="s">
         <v>20</v>
       </c>
       <c r="L80" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="M80" t="s">
         <v>22</v>
@@ -5415,49 +5415,49 @@
       <c r="O80" t="s">
         <v>25</v>
       </c>
-      <c r="P80" s="1">
-        <v>1862455</v>
+      <c r="P80" t="s">
+        <v>25</v>
       </c>
       <c r="Q80" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>69845984</v>
+        <v>69930297</v>
       </c>
       <c r="B81" s="2">
-        <v>46274.481273148151</v>
+        <v>46275.644074074073</v>
       </c>
       <c r="C81">
-        <v>69930862</v>
+        <v>70576373</v>
       </c>
       <c r="D81" s="2">
-        <v>46275.647939814815</v>
+        <v>46286.453009259261</v>
       </c>
       <c r="E81" t="s">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="F81" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G81">
-        <v>707730380</v>
+        <v>709090251</v>
       </c>
       <c r="H81" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I81" t="s">
         <v>25</v>
       </c>
       <c r="J81" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="K81" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="L81" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="M81" t="s">
         <v>22</v>
@@ -5477,40 +5477,40 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>69929747</v>
+        <v>69971411</v>
       </c>
       <c r="B82" s="2">
-        <v>46275.640439814815</v>
+        <v>46276.466805555552</v>
       </c>
       <c r="C82">
-        <v>70245971</v>
+        <v>70563629</v>
       </c>
       <c r="D82" s="2">
-        <v>46281.44803240741</v>
+        <v>46286.039155092592</v>
       </c>
       <c r="E82" t="s">
-        <v>225</v>
+        <v>47</v>
       </c>
       <c r="F82" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G82">
-        <v>709090251</v>
+        <v>708081900</v>
       </c>
       <c r="H82" t="s">
-        <v>227</v>
+        <v>111</v>
       </c>
       <c r="I82" t="s">
         <v>25</v>
       </c>
       <c r="J82" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="K82" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="L82" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="M82" t="s">
         <v>22</v>
@@ -5525,52 +5525,49 @@
         <v>25</v>
       </c>
       <c r="Q82" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>69930297</v>
+        <v>69993110</v>
       </c>
       <c r="B83" s="2">
-        <v>46275.644074074073</v>
+        <v>46276.635578703703</v>
       </c>
       <c r="C83">
-        <v>70246033</v>
+        <v>70111408</v>
       </c>
       <c r="D83" s="2">
-        <v>46281.448437500003</v>
+        <v>46279.481817129628</v>
       </c>
       <c r="E83" t="s">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="F83" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G83">
-        <v>709090251</v>
+        <v>711255757</v>
       </c>
       <c r="H83" t="s">
-        <v>228</v>
-      </c>
-      <c r="I83" t="s">
-        <v>25</v>
+        <v>223</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
       </c>
       <c r="J83" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="K83" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="L83" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="M83" t="s">
         <v>22</v>
       </c>
-      <c r="N83" t="s">
-        <v>23</v>
-      </c>
       <c r="O83" t="s">
         <v>25</v>
       </c>
@@ -5578,110 +5575,110 @@
         <v>25</v>
       </c>
       <c r="Q83" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>69971411</v>
+        <v>70111454</v>
       </c>
       <c r="B84" s="2">
-        <v>46276.466805555552</v>
+        <v>46279.482233796298</v>
       </c>
       <c r="C84">
-        <v>70275663</v>
+        <v>70253589</v>
       </c>
       <c r="D84" s="2">
-        <v>46281.667905092596</v>
+        <v>46281.505543981482</v>
       </c>
       <c r="E84" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="F84" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="G84">
-        <v>708081900</v>
+        <v>709489988</v>
       </c>
       <c r="H84" t="s">
-        <v>118</v>
+        <v>243</v>
       </c>
       <c r="I84" t="s">
         <v>25</v>
       </c>
       <c r="J84" t="s">
-        <v>53</v>
+        <v>244</v>
       </c>
       <c r="K84" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="L84" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="M84" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="N84" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O84" t="s">
         <v>25</v>
       </c>
-      <c r="P84" t="s">
-        <v>25</v>
+      <c r="P84" s="1">
+        <v>2362401</v>
       </c>
       <c r="Q84" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>69993110</v>
+        <v>70112153</v>
       </c>
       <c r="B85" s="2">
-        <v>46276.635578703703</v>
+        <v>46279.487187500003</v>
       </c>
       <c r="C85">
-        <v>70111408</v>
+        <v>70243714</v>
       </c>
       <c r="D85" s="2">
-        <v>46279.481817129628</v>
+        <v>46281.431145833332</v>
       </c>
       <c r="E85" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F85" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G85">
-        <v>711255757</v>
+        <v>700528536</v>
       </c>
       <c r="H85" t="s">
-        <v>231</v>
-      </c>
-      <c r="I85">
-        <v>0</v>
+        <v>226</v>
+      </c>
+      <c r="I85" t="s">
+        <v>25</v>
       </c>
       <c r="J85" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="K85" t="s">
-        <v>119</v>
+        <v>161</v>
       </c>
       <c r="L85" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="M85" t="s">
         <v>22</v>
       </c>
       <c r="N85" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O85" t="s">
         <v>25</v>
       </c>
-      <c r="P85" t="s">
-        <v>25</v>
+      <c r="P85" s="1">
+        <v>5000000</v>
       </c>
       <c r="Q85" t="s">
         <v>25</v>
@@ -5689,34 +5686,34 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>70111454</v>
+        <v>70175069</v>
       </c>
       <c r="B86" s="2">
-        <v>46279.482233796298</v>
+        <v>46280.429618055554</v>
       </c>
       <c r="C86">
-        <v>70253589</v>
+        <v>70392661</v>
       </c>
       <c r="D86" s="2">
-        <v>46281.505543981482</v>
+        <v>46283.360497685186</v>
       </c>
       <c r="E86" t="s">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="F86" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="G86">
-        <v>709489988</v>
+        <v>707389414</v>
       </c>
       <c r="H86" t="s">
-        <v>233</v>
-      </c>
-      <c r="I86">
-        <v>4123646</v>
+        <v>133</v>
+      </c>
+      <c r="I86" t="s">
+        <v>25</v>
       </c>
       <c r="J86" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K86" t="s">
         <v>20</v>
@@ -5725,45 +5722,45 @@
         <v>21</v>
       </c>
       <c r="M86" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="N86" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="O86" t="s">
         <v>25</v>
       </c>
       <c r="P86" s="1">
-        <v>2362401</v>
+        <v>800000</v>
       </c>
       <c r="Q86" t="s">
-        <v>234</v>
+        <v>46</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>70112153</v>
+        <v>70192793</v>
       </c>
       <c r="B87" s="2">
-        <v>46279.487187500003</v>
+        <v>46280.563958333332</v>
       </c>
       <c r="C87">
-        <v>70243714</v>
+        <v>70240923</v>
       </c>
       <c r="D87" s="2">
-        <v>46281.431145833332</v>
+        <v>46281.406319444446</v>
       </c>
       <c r="E87" t="s">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="F87" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G87">
-        <v>700528536</v>
+        <v>747504962</v>
       </c>
       <c r="H87" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="I87" t="s">
         <v>25</v>
@@ -5772,7 +5769,7 @@
         <v>29</v>
       </c>
       <c r="K87" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="L87" t="s">
         <v>21</v>
@@ -5787,7 +5784,7 @@
         <v>25</v>
       </c>
       <c r="P87" s="1">
-        <v>5000000</v>
+        <v>2200000</v>
       </c>
       <c r="Q87" t="s">
         <v>25</v>
@@ -5795,28 +5792,28 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>70175069</v>
+        <v>70205587</v>
       </c>
       <c r="B88" s="2">
-        <v>46280.429618055554</v>
+        <v>46280.659537037034</v>
       </c>
       <c r="C88">
-        <v>70392661</v>
+        <v>70563644</v>
       </c>
       <c r="D88" s="2">
-        <v>46283.360497685186</v>
+        <v>46286.040972222225</v>
       </c>
       <c r="E88" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="F88" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="G88">
-        <v>707389414</v>
+        <v>769563620</v>
       </c>
       <c r="H88" t="s">
-        <v>141</v>
+        <v>231</v>
       </c>
       <c r="I88" t="s">
         <v>25</v>
@@ -5840,36 +5837,36 @@
         <v>25</v>
       </c>
       <c r="P88" s="1">
-        <v>800000</v>
+        <v>500000</v>
       </c>
       <c r="Q88" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>70192793</v>
+        <v>70270437</v>
       </c>
       <c r="B89" s="2">
-        <v>46280.563958333332</v>
+        <v>46281.630682870367</v>
       </c>
       <c r="C89">
-        <v>70240923</v>
+        <v>70445294</v>
       </c>
       <c r="D89" s="2">
-        <v>46281.406319444446</v>
+        <v>46283.712384259263</v>
       </c>
       <c r="E89" t="s">
-        <v>225</v>
+        <v>66</v>
       </c>
       <c r="F89" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G89">
-        <v>747504962</v>
+        <v>707019933</v>
       </c>
       <c r="H89" t="s">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="I89" t="s">
         <v>25</v>
@@ -5878,7 +5875,7 @@
         <v>29</v>
       </c>
       <c r="K89" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="L89" t="s">
         <v>21</v>
@@ -5887,54 +5884,54 @@
         <v>22</v>
       </c>
       <c r="N89" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O89" t="s">
         <v>25</v>
       </c>
       <c r="P89" s="1">
-        <v>2200000</v>
+        <v>1000219</v>
       </c>
       <c r="Q89" t="s">
-        <v>25</v>
+        <v>233</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>70205587</v>
+        <v>70283035</v>
       </c>
       <c r="B90" s="2">
-        <v>46280.659537037034</v>
+        <v>46281.721631944441</v>
       </c>
       <c r="C90">
-        <v>70280140</v>
+        <v>70402116</v>
       </c>
       <c r="D90" s="2">
-        <v>46281.699675925927</v>
+        <v>46283.446388888886</v>
       </c>
       <c r="E90" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="F90" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="G90">
-        <v>769563620</v>
+        <v>758848035</v>
       </c>
       <c r="H90" t="s">
-        <v>242</v>
+        <v>111</v>
       </c>
       <c r="I90" t="s">
         <v>25</v>
       </c>
       <c r="J90" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="K90" t="s">
         <v>20</v>
       </c>
       <c r="L90" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="M90" t="s">
         <v>22</v>
@@ -5945,105 +5942,105 @@
       <c r="O90" t="s">
         <v>25</v>
       </c>
-      <c r="P90" s="1">
-        <v>500000</v>
+      <c r="P90" t="s">
+        <v>25</v>
       </c>
       <c r="Q90" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>70270437</v>
+        <v>70404284</v>
       </c>
       <c r="B91" s="2">
-        <v>46281.630682870367</v>
+        <v>46283.461597222224</v>
       </c>
       <c r="C91">
-        <v>70445294</v>
+        <v>70574470</v>
       </c>
       <c r="D91" s="2">
-        <v>46283.712384259263</v>
+        <v>46286.432488425926</v>
       </c>
       <c r="E91" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="F91" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G91">
-        <v>707019933</v>
+        <v>708047274</v>
       </c>
       <c r="H91" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="I91" t="s">
         <v>25</v>
       </c>
       <c r="J91" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="K91" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L91" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="M91" t="s">
         <v>22</v>
       </c>
       <c r="N91" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="O91" t="s">
         <v>25</v>
       </c>
-      <c r="P91" s="1">
-        <v>1000219</v>
+      <c r="P91" t="s">
+        <v>25</v>
       </c>
       <c r="Q91" t="s">
-        <v>244</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>70283035</v>
+        <v>70424921</v>
       </c>
       <c r="B92" s="2">
-        <v>46281.721631944441</v>
+        <v>46283.615347222221</v>
       </c>
       <c r="C92">
-        <v>70402116</v>
+        <v>70579023</v>
       </c>
       <c r="D92" s="2">
-        <v>46283.446388888886</v>
+        <v>46286.476030092592</v>
       </c>
       <c r="E92" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F92" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="G92">
-        <v>758848035</v>
+        <v>556658003</v>
       </c>
       <c r="H92" t="s">
-        <v>118</v>
+        <v>237</v>
       </c>
       <c r="I92" t="s">
         <v>25</v>
       </c>
       <c r="J92" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="K92" t="s">
         <v>20</v>
       </c>
       <c r="L92" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="M92" t="s">
-        <v>22</v>
+        <v>238</v>
       </c>
       <c r="N92" t="s">
         <v>23</v>
@@ -6051,52 +6048,52 @@
       <c r="O92" t="s">
         <v>25</v>
       </c>
-      <c r="P92" t="s">
-        <v>25</v>
+      <c r="P92" s="1">
+        <v>1605954</v>
       </c>
       <c r="Q92" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>70404284</v>
+        <v>70568121</v>
       </c>
       <c r="B93" s="2">
-        <v>46283.461597222224</v>
+        <v>46286.377245370371</v>
       </c>
       <c r="C93">
-        <v>70433692</v>
+        <v>70576938</v>
       </c>
       <c r="D93" s="2">
-        <v>46283.654224537036</v>
+        <v>46286.457615740743</v>
       </c>
       <c r="E93" t="s">
-        <v>247</v>
+        <v>81</v>
       </c>
       <c r="F93" t="s">
+        <v>245</v>
+      </c>
+      <c r="G93">
+        <v>708396352</v>
+      </c>
+      <c r="H93" t="s">
         <v>246</v>
       </c>
-      <c r="G93">
-        <v>708047274</v>
-      </c>
-      <c r="H93" t="s">
-        <v>118</v>
-      </c>
       <c r="I93" t="s">
         <v>25</v>
       </c>
       <c r="J93" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="K93" t="s">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="L93" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="M93" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="N93" t="s">
         <v>23</v>
@@ -6113,28 +6110,28 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>70424921</v>
+        <v>70568135</v>
       </c>
       <c r="B94" s="2">
-        <v>46283.615347222221</v>
+        <v>46286.377303240741</v>
       </c>
       <c r="C94">
-        <v>70424971</v>
+        <v>70576967</v>
       </c>
       <c r="D94" s="2">
-        <v>46283.615636574075</v>
+        <v>46286.458148148151</v>
       </c>
       <c r="E94" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="F94" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G94">
-        <v>556658003</v>
+        <v>708396352</v>
       </c>
       <c r="H94" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I94" t="s">
         <v>25</v>
@@ -6149,30 +6146,133 @@
         <v>21</v>
       </c>
       <c r="M94" t="s">
+        <v>106</v>
+      </c>
+      <c r="N94" t="s">
+        <v>23</v>
+      </c>
+      <c r="O94" t="s">
+        <v>25</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>70576572</v>
+      </c>
+      <c r="B95" s="2">
+        <v>46286.454629629632</v>
+      </c>
+      <c r="C95">
+        <v>70584702</v>
+      </c>
+      <c r="D95" s="2">
+        <v>46286.504004629627</v>
+      </c>
+      <c r="E95" t="s">
+        <v>249</v>
+      </c>
+      <c r="F95" t="s">
+        <v>247</v>
+      </c>
+      <c r="G95">
+        <v>545570737</v>
+      </c>
+      <c r="H95" t="s">
+        <v>248</v>
+      </c>
+      <c r="I95" t="s">
+        <v>25</v>
+      </c>
+      <c r="J95" t="s">
+        <v>36</v>
+      </c>
+      <c r="K95" t="s">
+        <v>20</v>
+      </c>
+      <c r="L95" t="s">
+        <v>37</v>
+      </c>
+      <c r="M95" t="s">
+        <v>22</v>
+      </c>
+      <c r="N95" t="s">
+        <v>23</v>
+      </c>
+      <c r="O95" t="s">
+        <v>25</v>
+      </c>
+      <c r="P95" s="1">
+        <v>1786800</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>70584651</v>
+      </c>
+      <c r="B96" s="2">
+        <v>46286.503865740742</v>
+      </c>
+      <c r="C96">
+        <v>70584747</v>
+      </c>
+      <c r="D96" s="2">
+        <v>46286.504189814812</v>
+      </c>
+      <c r="E96" t="s">
+        <v>107</v>
+      </c>
+      <c r="F96" t="s">
         <v>250</v>
       </c>
-      <c r="N94" t="s">
-        <v>23</v>
-      </c>
-      <c r="O94" t="s">
-        <v>25</v>
-      </c>
-      <c r="P94" s="1">
-        <v>1605954</v>
-      </c>
-      <c r="Q94" t="s">
+      <c r="G96">
+        <v>2722478730</v>
+      </c>
+      <c r="H96" t="s">
+        <v>251</v>
+      </c>
+      <c r="I96" t="s">
+        <v>25</v>
+      </c>
+      <c r="J96" t="s">
+        <v>29</v>
+      </c>
+      <c r="K96" t="s">
+        <v>20</v>
+      </c>
+      <c r="L96" t="s">
+        <v>21</v>
+      </c>
+      <c r="M96" t="s">
+        <v>22</v>
+      </c>
+      <c r="N96" t="s">
+        <v>23</v>
+      </c>
+      <c r="O96" t="s">
+        <v>25</v>
+      </c>
+      <c r="P96" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q96" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q94" xr:uid="{0B8238D3-B575-43CA-98BB-24C740F8E091}"/>
+  <autoFilter ref="A1:Q96" xr:uid="{10FFA819-8BFF-403A-B4F1-D40172154CE8}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Helvetica 75 Bold"&amp;8&amp;KED7D31 Orange Restricted</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>
 
